--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D660743C-0846-4F59-ADE4-F296F768E3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C3C036-C4FC-4239-904E-D303749A93F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2E94B379-50BD-40F2-B529-CD41B51C3ABA}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>对象</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>自动化测试构建补充</t>
+  </si>
+  <si>
+    <t>自动化测试扩展二期</t>
   </si>
 </sst>
 </file>
@@ -409,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70492BB-5D5A-4A89-8FE7-F27214D2061C}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -444,6 +447,14 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C3C036-C4FC-4239-904E-D303749A93F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7117B571-3119-4463-B738-EF7B96FA49DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2E94B379-50BD-40F2-B529-CD41B51C3ABA}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>对象</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>自动化测试扩展二期</t>
+  </si>
+  <si>
+    <t>慢测阈值收紧与覆盖率阈值</t>
   </si>
 </sst>
 </file>
@@ -412,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70492BB-5D5A-4A89-8FE7-F27214D2061C}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -458,6 +461,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -1,83 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7117B571-3119-4463-B738-EF7B96FA49DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2E94B379-50BD-40F2-B529-CD41B51C3ABA}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
-  <si>
-    <t>对象</t>
-  </si>
-  <si>
-    <t>通过</t>
-  </si>
-  <si>
-    <t>未通过</t>
-  </si>
-  <si>
-    <t>物品栏当前连接目标悬停截断</t>
-  </si>
-  <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>自动化测试扩展实现与命令说明补充</t>
-  </si>
-  <si>
-    <t>自动化测试构建补充</t>
-  </si>
-  <si>
-    <t>自动化测试扩展二期</t>
-  </si>
-  <si>
-    <t>慢测阈值收紧与覆盖率阈值</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -93,28 +51,87 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -414,63 +431,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70492BB-5D5A-4A89-8FE7-F27214D2061C}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>对象</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>未通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>物品栏当前连接目标悬停截断</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>自动化测试扩展实现与命令说明补充</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>自动化测试构建补充</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>自动化测试扩展二期</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>慢测阈值收紧与覆盖率阈值</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>跨区块调度与强制加载改动审查（含版本号更新）</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -9,14 +9,14 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -31,6 +31,12 @@
       <family val="2"/>
       <sz val="9"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,10 +61,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -436,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1">
@@ -516,18 +526,41 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="16.8" customHeight="1" s="2">
       <c r="A7" s="0" t="inlineStr">
         <is>
           <t>跨区块调度与强制加载改动审查（含版本号更新）</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.8" customHeight="1" s="2">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>遥控器去api依赖化</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>跨区块接管提示与策略改造</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -1,47 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A2DFAE-CED0-4CC5-ABF9-38479BA7F5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+  <si>
+    <t>对象</t>
+  </si>
+  <si>
+    <t>通过</t>
+  </si>
+  <si>
+    <t>未通过</t>
+  </si>
+  <si>
+    <t>物品栏当前连接目标悬停截断</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>自动化测试扩展实现与命令说明补充</t>
+  </si>
+  <si>
+    <t>自动化测试构建补充</t>
+  </si>
+  <si>
+    <t>自动化测试扩展二期</t>
+  </si>
+  <si>
+    <t>慢测阈值收紧与覆盖率阈值</t>
+  </si>
+  <si>
+    <t>跨区块调度与强制加载改动审查（含版本号更新）</t>
+  </si>
+  <si>
+    <t>遥控器去api依赖化</t>
+  </si>
+  <si>
+    <t>跨区块接管提示与策略改造</t>
+  </si>
+  <si>
+    <t>✓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块状态外显</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,91 +111,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -441,128 +435,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>对象</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>通过</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>未通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>物品栏当前连接目标悬停截断</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>自动化测试扩展实现与命令说明补充</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>自动化测试构建补充</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>自动化测试扩展二期</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>慢测阈值收紧与覆盖率阈值</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.8" customHeight="1" s="2">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>跨区块调度与强制加载改动审查（含版本号更新）</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.8" customHeight="1" s="2">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>遥控器去api依赖化</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>跨区块接管提示与策略改造</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A2DFAE-CED0-4CC5-ABF9-38479BA7F5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD615AB-E1D7-4440-A203-0ED3B53D12F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>对象</t>
   </si>
@@ -63,6 +63,14 @@
   </si>
   <si>
     <t>方块状态外显</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混合批量输入+结构化重建展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>✓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -436,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -522,6 +530,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="11" spans="1:3" ht="16.8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs_dev/审查日志.xlsx
+++ b/docs_dev/审查日志.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenProjects\RedstoneLink\rl-release-mixin-dust\docs_dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD615AB-E1D7-4440-A203-0ED3B53D12F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BB873C-C43D-4710-9057-AB330891F0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>对象</t>
   </si>
@@ -67,6 +67,10 @@
   </si>
   <si>
     <t>混合批量输入+结构化重建展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gui优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -444,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -535,7 +539,15 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
